--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/oct-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/oct-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC oct-2025" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC oct-2025" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2749,7 +2749,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3481,7 +3481,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3542,7 +3542,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3969,7 +3969,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4030,7 +4030,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4335,7 +4335,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4583,7 +4583,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4827,7 +4827,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5803,7 +5803,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5925,7 +5925,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5986,7 +5986,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6108,7 +6108,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6291,7 +6291,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6413,7 +6413,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7027,7 +7027,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7088,7 +7088,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7393,7 +7393,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7454,7 +7454,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7637,7 +7637,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7698,7 +7698,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7759,7 +7759,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7820,7 +7820,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7942,7 +7942,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8125,7 +8125,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8186,7 +8186,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8247,7 +8247,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8262,7 +8262,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8495,7 +8495,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8617,7 +8617,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8739,7 +8739,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8800,7 +8800,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8861,7 +8861,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8983,7 +8983,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9166,7 +9166,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9288,7 +9288,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9532,7 +9532,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9593,7 +9593,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9898,7 +9898,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10020,7 +10020,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10142,7 +10142,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10203,7 +10203,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10325,7 +10325,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10386,7 +10386,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10447,7 +10447,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10508,7 +10508,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10691,7 +10691,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10813,7 +10813,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10874,7 +10874,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11118,7 +11118,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11179,7 +11179,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11301,7 +11301,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11362,7 +11362,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11484,7 +11484,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11545,7 +11545,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11606,7 +11606,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11667,7 +11667,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11850,7 +11850,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12033,7 +12033,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12216,7 +12216,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12277,7 +12277,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12338,7 +12338,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12399,7 +12399,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12460,7 +12460,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12521,7 +12521,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12582,7 +12582,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12643,7 +12643,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12704,7 +12704,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12887,7 +12887,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12948,7 +12948,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -13009,7 +13009,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13070,7 +13070,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13131,7 +13131,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13192,7 +13192,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13253,7 +13253,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13436,7 +13436,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -13497,7 +13497,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13619,7 +13619,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13680,7 +13680,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13741,7 +13741,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13985,7 +13985,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14107,7 +14107,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14168,7 +14168,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14229,7 +14229,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14290,7 +14290,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14351,7 +14351,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14412,7 +14412,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14473,7 +14473,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14534,7 +14534,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14595,7 +14595,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14656,7 +14656,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14717,7 +14717,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/oct-2025.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/oct-2025.xlsx
@@ -562,7 +562,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1143,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1208,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1395,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1460,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1525,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1651,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1716,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1842,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1907,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1972,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2159,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2224,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2350,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2415,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2480,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2545,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2579,7 +2675,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2740,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2805,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2931,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +2996,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3122,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3187,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3189,7 +3313,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3439,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3433,7 +3565,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3494,7 +3630,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3616,7 +3756,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3677,7 +3821,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3738,7 +3886,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3860,7 +4012,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3982,7 +4138,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4043,7 +4203,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4104,7 +4268,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4165,7 +4333,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4226,7 +4398,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4348,7 +4524,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4409,7 +4589,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4718,7 +4902,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4840,7 +5028,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4901,7 +5093,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4962,7 +5158,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5084,7 +5284,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5206,7 +5410,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5267,7 +5475,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5389,7 +5601,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5450,7 +5666,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5511,7 +5731,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5694,7 +5918,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5755,7 +5983,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5816,7 +6048,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5877,7 +6113,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5938,7 +6178,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5999,7 +6243,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6121,7 +6369,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6243,7 +6495,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6304,7 +6560,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6365,7 +6625,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6487,7 +6751,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6548,7 +6816,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6670,7 +6942,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6731,7 +7007,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6792,7 +7072,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6918,7 +7202,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6979,7 +7267,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7040,7 +7332,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7101,7 +7397,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7162,7 +7462,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7223,7 +7527,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7284,7 +7592,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7345,7 +7657,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7406,7 +7722,11 @@
           <t>96.689.970-0</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7467,7 +7787,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7528,7 +7852,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7589,7 +7917,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7650,7 +7982,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7772,7 +8108,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7833,7 +8173,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7894,7 +8238,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8016,7 +8364,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8077,7 +8429,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8138,7 +8494,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8199,7 +8559,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8325,7 +8689,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8386,7 +8754,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8447,7 +8819,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8935,7 +9311,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8996,7 +9376,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9179,7 +9563,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9240,7 +9628,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9301,7 +9693,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9362,7 +9758,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9423,7 +9823,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9484,7 +9888,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9545,7 +9953,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9606,7 +10018,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9667,7 +10083,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9728,7 +10148,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9789,7 +10213,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9850,7 +10278,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9911,7 +10343,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9972,7 +10408,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10033,7 +10473,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10094,7 +10538,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10155,7 +10603,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10277,7 +10729,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10460,7 +10916,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10521,7 +10981,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10704,7 +11168,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10765,7 +11233,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10826,7 +11298,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10948,7 +11424,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11009,7 +11489,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11131,7 +11615,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11192,7 +11680,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11253,7 +11745,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11314,7 +11810,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11436,7 +11936,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11497,7 +12001,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11558,7 +12066,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11619,7 +12131,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11680,7 +12196,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11741,7 +12261,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11924,7 +12448,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12046,7 +12574,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12107,7 +12639,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12168,7 +12704,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12290,7 +12830,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12351,7 +12895,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12412,7 +12960,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12473,7 +13025,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12534,7 +13090,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12595,7 +13155,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12656,7 +13220,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12717,7 +13285,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12778,7 +13350,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12839,7 +13415,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12900,7 +13480,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12961,7 +13545,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13022,7 +13610,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13144,7 +13736,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13205,7 +13801,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13266,7 +13866,11 @@
           <t>76.376.530-k</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13510,7 +14114,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13571,7 +14179,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13632,7 +14244,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13754,7 +14370,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13876,7 +14496,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13937,7 +14561,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14059,7 +14687,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14120,7 +14752,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14181,7 +14817,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14242,7 +14882,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14303,7 +14947,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14364,7 +15012,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14425,7 +15077,11 @@
           <t>96.693.120-5</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14669,7 +15325,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
